--- a/sources/table_normalization/xlsx/education-table25.xlsx
+++ b/sources/table_normalization/xlsx/education-table25.xlsx
@@ -264,10 +264,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
-    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="#,##0_)"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0_)"/>
-    <numFmt numFmtId="170" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="#,##0_)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -661,7 +661,7 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
@@ -678,93 +678,54 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="2" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5"/>
     <xf numFmtId="37" fontId="1" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="1" fillId="2" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="1" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="1" fillId="2" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="1" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="3" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -772,24 +733,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="3" borderId="17" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="25" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="26" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
@@ -799,6 +742,63 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="25" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="26" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1157,21 +1157,21 @@
       <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="47" t="s">
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="48" t="s">
+      <c r="J1" s="47" t="s">
         <v>4</v>
       </c>
       <c r="K1" s="22"/>
@@ -1180,46 +1180,46 @@
       <c r="N1" s="22"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="25" customHeight="1">
-      <c r="A2" s="40"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="34" t="s">
+      <c r="A2" s="39"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="36" t="s">
+      <c r="D2" s="51"/>
+      <c r="E2" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="35"/>
-      <c r="G2" s="37" t="s">
+      <c r="F2" s="51"/>
+      <c r="G2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="35"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="50"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="48"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="42"/>
+      <c r="A3" s="40"/>
       <c r="B3" s="43"/>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="46" t="s">
+      <c r="E3" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="46" t="s">
+      <c r="G3" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="51"/>
-      <c r="J3" s="52"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="49"/>
     </row>
     <row r="4" spans="1:14" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -2887,83 +2887,83 @@
       </c>
     </row>
     <row r="56" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A56" s="53" t="str">
+      <c r="A56" s="34" t="str">
         <f>CONCATENATE("NOTE: Table reads (for US Totals):  Of all ",IF(ISTEXT(B4),LEFT(B4,3),TEXT(B4,"#,##0"))," public schools with any grade 9-12 (or ungraded), ",IF(ISTEXT(C4),LEFT(C4,3),TEXT(C4,"#,##0"))," (",TEXT(D4,"0.0"),"%) offered biology classes.")</f>
         <v>NOTE: Table reads (for US Totals):  Of all 47,796 public schools with any grade 9-12 (or ungraded), 22,597 (47.3%) offered biology classes.</v>
       </c>
-      <c r="B56" s="54"/>
-      <c r="C56" s="54"/>
-      <c r="D56" s="54"/>
-      <c r="E56" s="54"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="54"/>
-      <c r="H56" s="54"/>
-      <c r="I56" s="54"/>
-      <c r="J56" s="54"/>
-      <c r="K56" s="54"/>
-      <c r="L56" s="54"/>
-      <c r="M56" s="54"/>
-      <c r="N56" s="54"/>
-      <c r="O56" s="54"/>
-      <c r="P56" s="54"/>
-      <c r="Q56" s="54"/>
-      <c r="R56" s="54"/>
-      <c r="S56" s="54"/>
-      <c r="T56" s="54"/>
-      <c r="U56" s="55"/>
-      <c r="V56" s="55"/>
+      <c r="B56" s="35"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="35"/>
+      <c r="J56" s="35"/>
+      <c r="K56" s="35"/>
+      <c r="L56" s="35"/>
+      <c r="M56" s="35"/>
+      <c r="N56" s="35"/>
+      <c r="O56" s="35"/>
+      <c r="P56" s="35"/>
+      <c r="Q56" s="35"/>
+      <c r="R56" s="35"/>
+      <c r="S56" s="35"/>
+      <c r="T56" s="35"/>
+      <c r="U56" s="36"/>
+      <c r="V56" s="36"/>
     </row>
     <row r="57" spans="1:22" s="3" customFormat="1" ht="14.15" customHeight="1">
-      <c r="A57" s="56" t="s">
+      <c r="A57" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="B57" s="56"/>
-      <c r="C57" s="56"/>
-      <c r="D57" s="56"/>
-      <c r="E57" s="56"/>
-      <c r="F57" s="56"/>
-      <c r="G57" s="56"/>
-      <c r="H57" s="56"/>
-      <c r="I57" s="56"/>
-      <c r="J57" s="56"/>
-      <c r="K57" s="56"/>
-      <c r="L57" s="56"/>
-      <c r="M57" s="56"/>
-      <c r="N57" s="56"/>
-      <c r="O57" s="56"/>
-      <c r="P57" s="56"/>
-      <c r="Q57" s="56"/>
-      <c r="R57" s="56"/>
-      <c r="S57" s="56"/>
-      <c r="T57" s="56"/>
-      <c r="U57" s="56"/>
-      <c r="V57" s="56"/>
+      <c r="B57" s="37"/>
+      <c r="C57" s="37"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="37"/>
+      <c r="H57" s="37"/>
+      <c r="I57" s="37"/>
+      <c r="J57" s="37"/>
+      <c r="K57" s="37"/>
+      <c r="L57" s="37"/>
+      <c r="M57" s="37"/>
+      <c r="N57" s="37"/>
+      <c r="O57" s="37"/>
+      <c r="P57" s="37"/>
+      <c r="Q57" s="37"/>
+      <c r="R57" s="37"/>
+      <c r="S57" s="37"/>
+      <c r="T57" s="37"/>
+      <c r="U57" s="37"/>
+      <c r="V57" s="37"/>
     </row>
     <row r="58" spans="1:22" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A58" s="56" t="s">
+      <c r="A58" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B58" s="56"/>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="56"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="56"/>
-      <c r="I58" s="56"/>
-      <c r="J58" s="56"/>
-      <c r="K58" s="56"/>
-      <c r="L58" s="56"/>
-      <c r="M58" s="56"/>
-      <c r="N58" s="56"/>
-      <c r="O58" s="56"/>
-      <c r="P58" s="56"/>
-      <c r="Q58" s="56"/>
-      <c r="R58" s="56"/>
-      <c r="S58" s="56"/>
-      <c r="T58" s="56"/>
-      <c r="U58" s="56"/>
-      <c r="V58" s="56"/>
+      <c r="B58" s="37"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
+      <c r="H58" s="37"/>
+      <c r="I58" s="37"/>
+      <c r="J58" s="37"/>
+      <c r="K58" s="37"/>
+      <c r="L58" s="37"/>
+      <c r="M58" s="37"/>
+      <c r="N58" s="37"/>
+      <c r="O58" s="37"/>
+      <c r="P58" s="37"/>
+      <c r="Q58" s="37"/>
+      <c r="R58" s="37"/>
+      <c r="S58" s="37"/>
+      <c r="T58" s="37"/>
+      <c r="U58" s="37"/>
+      <c r="V58" s="37"/>
     </row>
   </sheetData>
   <sortState ref="A8:J58">
